--- a/banka/kuveytturk.xlsx
+++ b/banka/kuveytturk.xlsx
@@ -44,10 +44,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,#00.00;[RED]\-#,#00.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -76,6 +77,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,17 +133,29 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -265,32 +286,664 @@
   <sheetFormatPr defaultColWidth="8.82421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="31.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="16.26"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="2" width="8.82"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="1047576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047723" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047724" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047726" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047760" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047762" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047765" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047766" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047767" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047768" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047769" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047770" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047771" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047772" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047774" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047775" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047777" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047780" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047781" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047782" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047783" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047784" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047786" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047787" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047788" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047789" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047790" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047792" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047793" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047795" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047796" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047797" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047798" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047799" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047800" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047801" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047804" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047805" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047807" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047808" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047814" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047816" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047817" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047819" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047820" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047825" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047861" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047862" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047876" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047877" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1047999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048022" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048092" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048094" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048097" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
